--- a/artfynd/A 14132-2026 artfynd.xlsx
+++ b/artfynd/A 14132-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122747824</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,12 +765,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -784,12 +779,7 @@
         <v>122747836</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,12 +866,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -890,12 +880,7 @@
         <v>122743169</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,12 +967,12 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -996,12 +981,7 @@
         <v>122747834</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,12 +1068,12 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1102,12 +1082,7 @@
         <v>122747833</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,12 +1169,12 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1208,12 +1183,7 @@
         <v>122747826</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,12 +1270,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 14132-2026 artfynd.xlsx
+++ b/artfynd/A 14132-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747824</v>
       </c>
       <c r="B2" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747836</v>
       </c>
       <c r="B3" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122743169</v>
       </c>
       <c r="B4" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122747834</v>
       </c>
       <c r="B5" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122747833</v>
       </c>
       <c r="B6" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122747826</v>
       </c>
       <c r="B7" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14132-2026 artfynd.xlsx
+++ b/artfynd/A 14132-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747824</v>
       </c>
       <c r="B2" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747836</v>
       </c>
       <c r="B3" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122743169</v>
       </c>
       <c r="B4" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122747834</v>
       </c>
       <c r="B5" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122747833</v>
       </c>
       <c r="B6" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122747826</v>
       </c>
       <c r="B7" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14132-2026 artfynd.xlsx
+++ b/artfynd/A 14132-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747824</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747836</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122743169</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122747834</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122747833</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122747826</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14132-2026 artfynd.xlsx
+++ b/artfynd/A 14132-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743168</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743169</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747824</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747826</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747833</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747834</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,8 +1414,22 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747836</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>